--- a/app/ReportGeneration/TemplateData.xlsx
+++ b/app/ReportGeneration/TemplateData.xlsx
@@ -478,7 +478,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45097</v>
+        <v>45644</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -497,7 +497,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45097.01041666666</v>
+        <v>45644.01041666666</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
@@ -516,7 +516,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45097.02083333334</v>
+        <v>45644.02083333334</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
@@ -535,7 +535,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45097.03125</v>
+        <v>45644.03125</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
@@ -554,7 +554,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45097.04166666666</v>
+        <v>45644.04166666666</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
@@ -573,7 +573,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45097.05208333334</v>
+        <v>45644.05208333334</v>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
@@ -592,7 +592,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45097.0625</v>
+        <v>45644.0625</v>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
@@ -611,7 +611,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45097.07291666666</v>
+        <v>45644.07291666666</v>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -630,7 +630,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45097.08333333334</v>
+        <v>45644.08333333334</v>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -649,7 +649,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45097.09375</v>
+        <v>45644.09375</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -668,7 +668,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45097.10416666666</v>
+        <v>45644.10416666666</v>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -687,7 +687,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45097.11458333334</v>
+        <v>45644.11458333334</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -706,7 +706,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45097.125</v>
+        <v>45644.125</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -725,7 +725,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45097.13541666666</v>
+        <v>45644.13541666666</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -744,7 +744,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45097.14583333334</v>
+        <v>45644.14583333334</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -763,7 +763,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45097.15625</v>
+        <v>45644.15625</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -782,7 +782,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45097.16666666666</v>
+        <v>45644.16666666666</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -801,7 +801,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45097.17708333334</v>
+        <v>45644.17708333334</v>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -820,7 +820,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45097.1875</v>
+        <v>45644.1875</v>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -839,7 +839,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45097.19791666666</v>
+        <v>45644.19791666666</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
@@ -858,7 +858,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45097.20833333334</v>
+        <v>45644.20833333334</v>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
@@ -877,7 +877,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45097.21875</v>
+        <v>45644.21875</v>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
@@ -896,7 +896,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45097.22916666666</v>
+        <v>45644.22916666666</v>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
@@ -915,7 +915,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45097.23958333334</v>
+        <v>45644.23958333334</v>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
@@ -934,7 +934,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45097.25</v>
+        <v>45644.25</v>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
@@ -953,7 +953,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45097.26041666666</v>
+        <v>45644.26041666666</v>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
@@ -972,7 +972,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45097.27083333334</v>
+        <v>45644.27083333334</v>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
@@ -991,7 +991,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45097.28125</v>
+        <v>45644.28125</v>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45097.29166666666</v>
+        <v>45644.29166666666</v>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45097.30208333334</v>
+        <v>45644.30208333334</v>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45097.3125</v>
+        <v>45644.3125</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45097.32291666666</v>
+        <v>45644.32291666666</v>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45097.33333333334</v>
+        <v>45644.33333333334</v>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45097.34375</v>
+        <v>45644.34375</v>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45097.35416666666</v>
+        <v>45644.35416666666</v>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45097.36458333334</v>
+        <v>45644.36458333334</v>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45097.375</v>
+        <v>45644.375</v>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45097.38541666666</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45097.39583333334</v>
+        <v>45644.39583333334</v>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45097.40625</v>
+        <v>45644.40625</v>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45097.41666666666</v>
+        <v>45644.41666666666</v>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45097.42708333334</v>
+        <v>45644.42708333334</v>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45097.4375</v>
+        <v>45644.4375</v>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45097.44791666666</v>
+        <v>45644.44791666666</v>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45097.45833333334</v>
+        <v>45644.45833333334</v>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45097.46875</v>
+        <v>45644.46875</v>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45097.47916666666</v>
+        <v>45644.47916666666</v>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45097.48958333334</v>
+        <v>45644.48958333334</v>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45097.5</v>
+        <v>45644.5</v>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45097.51041666666</v>
+        <v>45644.51041666666</v>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45097.52083333334</v>
+        <v>45644.52083333334</v>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45097.53125</v>
+        <v>45644.53125</v>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45097.54166666666</v>
+        <v>45644.54166666666</v>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45097.55208333334</v>
+        <v>45644.55208333334</v>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45097.5625</v>
+        <v>45644.5625</v>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45097.57291666666</v>
+        <v>45644.57291666666</v>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45097.58333333334</v>
+        <v>45644.58333333334</v>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45097.59375</v>
+        <v>45644.59375</v>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45097.60416666666</v>
+        <v>45644.60416666666</v>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45097.61458333334</v>
+        <v>45644.61458333334</v>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45097.625</v>
+        <v>45644.625</v>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45097.63541666666</v>
+        <v>45644.63541666666</v>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45097.64583333334</v>
+        <v>45644.64583333334</v>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45097.65625</v>
+        <v>45644.65625</v>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45097.66666666666</v>
+        <v>45644.66666666666</v>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45097.67708333334</v>
+        <v>45644.67708333334</v>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45097.6875</v>
+        <v>45644.6875</v>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45097.69791666666</v>
+        <v>45644.69791666666</v>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45097.70833333334</v>
+        <v>45644.70833333334</v>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45097.71875</v>
+        <v>45644.71875</v>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45097.72916666666</v>
+        <v>45644.72916666666</v>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45097.73958333334</v>
+        <v>45644.73958333334</v>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45097.75</v>
+        <v>45644.75</v>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45097.76041666666</v>
+        <v>45644.76041666666</v>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45097.77083333334</v>
+        <v>45644.77083333334</v>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45097.78125</v>
+        <v>45644.78125</v>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45097.79166666666</v>
+        <v>45644.79166666666</v>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45097.80208333334</v>
+        <v>45644.80208333334</v>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45097.8125</v>
+        <v>45644.8125</v>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45097.82291666666</v>
+        <v>45644.82291666666</v>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45097.83333333334</v>
+        <v>45644.83333333334</v>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45097.84375</v>
+        <v>45644.84375</v>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45097.85416666666</v>
+        <v>45644.85416666666</v>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45097.86458333334</v>
+        <v>45644.86458333334</v>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45097.875</v>
+        <v>45644.875</v>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
@@ -2093,7 +2093,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45097.88541666666</v>
+        <v>45644.88541666666</v>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45097.89583333334</v>
+        <v>45644.89583333334</v>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45097.90625</v>
+        <v>45644.90625</v>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45097.91666666666</v>
+        <v>45644.91666666666</v>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45097.92708333334</v>
+        <v>45644.92708333334</v>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45097.9375</v>
+        <v>45644.9375</v>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45097.94791666666</v>
+        <v>45644.94791666666</v>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45097.95833333334</v>
+        <v>45644.95833333334</v>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45097.96875</v>
+        <v>45644.96875</v>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45097.97916666666</v>
+        <v>45644.97916666666</v>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45097.98958333334</v>
+        <v>45644.98958333334</v>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
